--- a/ctl-site/src/assets/PROJETOS/PROJETO_3.xlsx
+++ b/ctl-site/src/assets/PROJETOS/PROJETO_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\ctl-site\ctl-site\src\assets\PROJETOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9be54d10f24db4ff/CTL site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246DDCED-61B3-4F5C-BEBF-B67DF1130C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F9E3592-5CDF-42D4-8212-940345C9F36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet_TEST_1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -37,30 +37,10 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -72,7 +52,7 @@
     <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum.</t>
   </si>
   <si>
-    <t>Título Projeto 3</t>
+    <t>CTL Concilia</t>
   </si>
 </sst>
 </file>
@@ -168,17 +148,9 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <rv s="0">
     <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -196,8 +168,6 @@
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -465,15 +435,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="59.33203125" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" customWidth="1"/>
-    <col min="4" max="4" width="37.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="59.28515625" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="113.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -484,17 +454,9 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ctl-site/src/assets/PROJETOS/PROJETO_3.xlsx
+++ b/ctl-site/src/assets/PROJETOS/PROJETO_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9be54d10f24db4ff/CTL site/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\ctl-site\ctl-site\src\assets\PROJETOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F9E3592-5CDF-42D4-8212-940345C9F36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83658006-BC73-4E87-A586-AF08C7D46EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet_TEST_1" sheetId="1" r:id="rId1"/>
@@ -47,19 +47,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum.</t>
   </si>
   <si>
     <t>CTL Concilia</t>
+  </si>
+  <si>
+    <t>TÍTULO
+Aparece no cartão e na dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIÇÃO
+Aparece no cartão e dialog. </t>
+  </si>
+  <si>
+    <t>IMAGENS
+A primeira aparece no cartão.
+As seguintes aparecem no carrossel da dialog.</t>
+  </si>
+  <si>
+    <t>LINK YOUTUBE
+Substitui o carrossel da dialog.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WvZiYpn2Py4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,16 +87,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -84,12 +118,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,29 +489,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
-    <col min="2" max="2" width="59.28515625" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" customWidth="1"/>
-    <col min="4" max="4" width="37.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="3" width="59.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="113.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="e" vm="1">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:3" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:4" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
